--- a/DesignData/Area.xlsx
+++ b/DesignData/Area.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,46 +485,6 @@
           <t>MonsterRespawnSec</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>CenterX</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CenterY</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CenterZ</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>HalfExtentX</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>HalfExtentY</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>RespawnX</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>RespawnY</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>RespawnZ</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -567,46 +527,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>float?</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>float?</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>float?</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -649,46 +569,6 @@
           <t>server</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -729,46 +609,6 @@
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>몬스터가 다시 나오는 시간(초). 0 이상이다</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>지역 중심의 X 좌표</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>지역 중심의 Y 좌표</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>지역 중심의 Z 좌표</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>중심에서 X 방향 반경. 0보다 크다</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>중심에서 Y 방향 반경. 0보다 크다</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>리스폰 지점의 X 좌표. 리스폰 지점이 없으면 비워 둔다</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>리스폰 지점의 Y 좌표</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>리스폰 지점의 Z 좌표</t>
         </is>
       </c>
     </row>
@@ -798,30 +638,6 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -854,21 +670,6 @@
       <c r="H6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2500</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -901,21 +702,6 @@
       <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2500</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -947,21 +733,6 @@
       </c>
       <c r="H8" t="n">
         <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2500</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Area.xlsx
+++ b/DesignData/Area.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -431,17 +431,6 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,21 +459,6 @@
           <t>HasRespawnPoint</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Monsters</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MaxMonsterCount</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>MonsterRespawnSec</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -512,21 +486,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ref[]:Monster</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -554,21 +513,6 @@
           <t>both</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -594,21 +538,6 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>리스폰 지점이 있으면 TRUE. 리스폰 지점이 있는 지역(마을)은 하나뿐이다</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>나오는 몬스터. ';'로 구분한다. 비어 있으면 몬스터가 나오지 않는다</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>동시에 있는 몬스터의 최대 수. 0 이상이다</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>몬스터가 다시 나오는 시간(초). 0 이상이다</t>
         </is>
       </c>
     </row>
@@ -632,12 +561,6 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -659,17 +582,6 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5000;5001;5002</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,17 +603,6 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>5003;5004;5005</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -722,17 +623,6 @@
       </c>
       <c r="E8" t="b">
         <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5006;5007;5008</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
